--- a/crm/v2/lgo/integral-top200-lgpi.xlsx
+++ b/crm/v2/lgo/integral-top200-lgpi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogue'!$A$1:$B$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogue'!$A$1:$C$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,12 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,11 +429,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B201"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,6 +448,11 @@
           <t>DESIGNATION</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PRIX NET HT</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -458,6 +465,9 @@
           <t>KARDEGIC 75MG PDR SACH 30</t>
         </is>
       </c>
+      <c r="C2" s="3" t="n">
+        <v>1.29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -470,6 +480,9 @@
           <t>IZALGI 500MG/25MG GELU BT16</t>
         </is>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -482,6 +495,9 @@
           <t>DIPROSTENE INJ SERING1ML 1</t>
         </is>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>3.71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -494,6 +510,9 @@
           <t>THEALOSE SOL OPHT FL 15ML T</t>
         </is>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>8.34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -506,6 +525,9 @@
           <t>KARDEGIC 160MG PDR SACH 30</t>
         </is>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>1.29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -518,6 +540,9 @@
           <t>LAMALINE GELU BT16</t>
         </is>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -530,6 +555,9 @@
           <t>SPASFON CPR BT30</t>
         </is>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -542,6 +570,9 @@
           <t>MOUNJARO 5MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>212.74</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -554,6 +585,9 @@
           <t>HELICIDINE 10% S/S SIR FP250ML</t>
         </is>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>2.34</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -566,6 +600,9 @@
           <t>DIFFU-K 600MG GELU BT40</t>
         </is>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -578,6 +615,9 @@
           <t>MOUNJARO 2,5MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>157.36</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -590,6 +630,9 @@
           <t>VENTOLINE 100MCG INH FL200DOS 1</t>
         </is>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>3.06</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -602,6 +645,9 @@
           <t>VISMED MULTI GTT LUBR FL15ML T</t>
         </is>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -614,6 +660,9 @@
           <t>HYLO CONFORT+COLLY HYD F10ML T</t>
         </is>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>7.02</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -626,6 +675,9 @@
           <t>SKIACOL 0,5% COLLY FL0,5ML</t>
         </is>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>7.11</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -638,6 +690,9 @@
           <t>GARDASIL 9 INJ SRG0,5ML 1+2AIG</t>
         </is>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -650,6 +705,9 @@
           <t>STERDEX POM OPHT UNIDOS 12</t>
         </is>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>1.73</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -662,6 +720,9 @@
           <t>NORMACOL LAVEMENT AD. D.130ML</t>
         </is>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -674,6 +735,9 @@
           <t>IBUFETUM 5% GEL TB60G</t>
         </is>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -686,6 +750,9 @@
           <t>BEXSERO INJ SRG0,5ML 1 +AIG</t>
         </is>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>70.51000000000001</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -698,6 +765,9 @@
           <t>ANTADYS 100MG CPR BT15</t>
         </is>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -710,6 +780,9 @@
           <t>EDUCTYL AD. SUP EFFV BT12</t>
         </is>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>1.29</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -722,6 +795,9 @@
           <t>SPASFON LYOC 80MG LYOT ORAL 10</t>
         </is>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -734,6 +810,9 @@
           <t>SLINDA 4MG CPR PELLIC BT28X3</t>
         </is>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>26.16</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -746,6 +825,9 @@
           <t>GAVISCON BUV SUSP SACH10ML 24</t>
         </is>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>3.42</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -758,6 +840,9 @@
           <t>VIT B12 DEL.1000MCG INJ A.2ML 6</t>
         </is>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>2.14</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -770,6 +855,9 @@
           <t>ZYMAD 10000UI/ML BUV GTT 10ML</t>
         </is>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>1.53</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -782,6 +870,9 @@
           <t>DACUDOSES OPHT UNIDOS10ML 24</t>
         </is>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -794,6 +885,9 @@
           <t>FLUVERMAL CPR BT6</t>
         </is>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>2.02</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -806,6 +900,9 @@
           <t>SHINGRIX INJ FL+FL 1</t>
         </is>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>168.39</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -818,6 +915,9 @@
           <t>LEVOTHYROX 25MCG CPR BT30 EXC</t>
         </is>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -830,6 +930,9 @@
           <t>EYLEA 114,3MG/ML INJ SRG 1</t>
         </is>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>352.02</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -842,6 +945,9 @@
           <t>LEVOTHYROX 75MCG CPR BT30 EXC</t>
         </is>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -854,6 +960,9 @@
           <t>SPIFEN 400MG CPR BT20</t>
         </is>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>1.56</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -866,6 +975,9 @@
           <t>REPATHA 140MG INJ STYLO1ML 1</t>
         </is>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>164.44</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -878,6 +990,9 @@
           <t>FLECTOR 1% GEL FL100G</t>
         </is>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>2.24</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -890,6 +1005,9 @@
           <t>OPTIVE  FUSION COLLYRE FL 10 ML</t>
         </is>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>5.61</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -902,6 +1020,9 @@
           <t>MONOPROST 50MCG/ML COLLY DOS30</t>
         </is>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>7.33</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -914,6 +1035,9 @@
           <t>DOLIPRANE 2,4% BUV FV100ML 1</t>
         </is>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -926,6 +1050,9 @@
           <t>ELUDRILPERIO BAIN BCHE FL200ML</t>
         </is>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>2.02</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -938,6 +1065,9 @@
           <t>LEVOTHYROX 50MCG CPR BT30 EXC</t>
         </is>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -950,6 +1080,9 @@
           <t>METEOSPASMYL CAPS BT20</t>
         </is>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>2.18</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -962,6 +1095,9 @@
           <t>LEVOTHYROX 100MCG CPR BT30 EXC</t>
         </is>
       </c>
+      <c r="C44" s="3" t="n">
+        <v>1.59</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -974,6 +1110,9 @@
           <t>NEOVIS TOT MULTI GTT FL15ML T</t>
         </is>
       </c>
+      <c r="C45" s="3" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -986,6 +1125,9 @@
           <t>FLUVERMAL 2% BUV FL30ML</t>
         </is>
       </c>
+      <c r="C46" s="3" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -998,6 +1140,9 @@
           <t>VISMED GEL MULTI GTT LUBR FL15ML (NEW)</t>
         </is>
       </c>
+      <c r="C47" s="3" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1010,6 +1155,9 @@
           <t>MOUNJARO 7,5MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
+      <c r="C48" s="3" t="n">
+        <v>301.11</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1022,6 +1170,9 @@
           <t>STAGID 700MG CPR BT30</t>
         </is>
       </c>
+      <c r="C49" s="3" t="n">
+        <v>1.76</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1034,6 +1185,9 @@
           <t>DERINOX SOL NAS FL15ML +POMP</t>
         </is>
       </c>
+      <c r="C50" s="3" t="n">
+        <v>4.43</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1046,6 +1200,9 @@
           <t>VAXNEUVANCE</t>
         </is>
       </c>
+      <c r="C51" s="3" t="n">
+        <v>43.39</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1058,6 +1215,9 @@
           <t>CLARADOL 500MG CAFEINE CPR 16</t>
         </is>
       </c>
+      <c r="C52" s="3" t="n">
+        <v>1.15</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1070,6 +1230,9 @@
           <t>INDOCOLLYRE 0,1% COLLY DOS 20</t>
         </is>
       </c>
+      <c r="C53" s="3" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1082,6 +1245,9 @@
           <t>METEOXANE GELU BT60</t>
         </is>
       </c>
+      <c r="C54" s="3" t="n">
+        <v>2.72</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1094,6 +1260,9 @@
           <t>REPEVAX INJ SRG 1 S/A+1</t>
         </is>
       </c>
+      <c r="C55" s="3" t="n">
+        <v>19.17</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1106,6 +1275,9 @@
           <t>AZYTER COLLY UNIDOS 6</t>
         </is>
       </c>
+      <c r="C56" s="3" t="n">
+        <v>4.12</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1118,6 +1290,9 @@
           <t>TARDYFERON 80MG CPR BT30</t>
         </is>
       </c>
+      <c r="C57" s="3" t="n">
+        <v>2.27</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1130,6 +1305,9 @@
           <t>NIMENRIX INJ FL+SRG 1 A/2AIG</t>
         </is>
       </c>
+      <c r="C58" s="3" t="n">
+        <v>34.8</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1142,6 +1320,9 @@
           <t>TRULICITY 1,5MG INJ STY0,5ML 4</t>
         </is>
       </c>
+      <c r="C59" s="3" t="n">
+        <v>71.42</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1154,6 +1335,9 @@
           <t>OZEMPIC 1MG INJ STYLO3ML 1</t>
         </is>
       </c>
+      <c r="C60" s="3" t="n">
+        <v>68.25</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1166,6 +1350,9 @@
           <t>LEVOTHYROX 75MCG CPR BT90 EXC</t>
         </is>
       </c>
+      <c r="C61" s="3" t="n">
+        <v>3.45</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1178,6 +1365,9 @@
           <t>LOCOID 0,1% CR TB30G</t>
         </is>
       </c>
+      <c r="C62" s="3" t="n">
+        <v>2.17</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1190,6 +1380,9 @@
           <t>DOLIPRANE 1000MG CPR BT8</t>
         </is>
       </c>
+      <c r="C63" s="3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1202,6 +1395,9 @@
           <t>VIT B12 GERDA 1000MCG AMP4ML 6</t>
         </is>
       </c>
+      <c r="C64" s="3" t="n">
+        <v>2.14</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1214,6 +1410,9 @@
           <t>ASPEGIC BB. 100MG BUV SACH 20</t>
         </is>
       </c>
+      <c r="C65" s="3" t="n">
+        <v>1.17</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1226,6 +1425,9 @@
           <t>WEGOVY 0,25MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
+      <c r="C66" s="3" t="n">
+        <v>131.21</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1238,6 +1440,9 @@
           <t>PANOTILE GTT AURIC FL8ML</t>
         </is>
       </c>
+      <c r="C67" s="3" t="n">
+        <v>1.42</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1250,6 +1455,9 @@
           <t>LEVOTHYROX 50MCG CPR BT90 EXC</t>
         </is>
       </c>
+      <c r="C68" s="3" t="n">
+        <v>2.31</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1262,6 +1470,9 @@
           <t>ASPIRINE PROTECT 100MG CPR 30</t>
         </is>
       </c>
+      <c r="C69" s="3" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1274,6 +1485,9 @@
           <t>DOLIPRANE 500MG PDR SACH 12</t>
         </is>
       </c>
+      <c r="C70" s="3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1286,6 +1500,9 @@
           <t>LEXOMIL 6MG CPR TB30</t>
         </is>
       </c>
+      <c r="C71" s="3" t="n">
+        <v>1.35</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1298,6 +1515,9 @@
           <t>ELIXYA SOL OPHT HYD FL 10ML T</t>
         </is>
       </c>
+      <c r="C72" s="3" t="n">
+        <v>6.21</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -1310,6 +1530,9 @@
           <t>LEVOTHYROX 125MCG CPR BT30 EXC</t>
         </is>
       </c>
+      <c r="C73" s="3" t="n">
+        <v>1.95</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -1322,6 +1545,9 @@
           <t>RHINOMAXIL 100MCG NAS PULV120D.</t>
         </is>
       </c>
+      <c r="C74" s="3" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -1334,6 +1560,9 @@
           <t>TRIDESONIT 0,05% CR TB30G</t>
         </is>
       </c>
+      <c r="C75" s="3" t="n">
+        <v>1.51</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -1346,6 +1575,9 @@
           <t>FUNGIZONE 10% BUV FL40ML</t>
         </is>
       </c>
+      <c r="C76" s="3" t="n">
+        <v>4.23</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -1358,6 +1590,9 @@
           <t>DOLIPRANE 1000MG GELU BT8</t>
         </is>
       </c>
+      <c r="C77" s="3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -1370,6 +1605,9 @@
           <t>DOLIPRANE 1000MG BUV SACH 8</t>
         </is>
       </c>
+      <c r="C78" s="3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -1382,6 +1620,9 @@
           <t>COUMADINE 2MG CPR BT20</t>
         </is>
       </c>
+      <c r="C79" s="3" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -1394,6 +1635,9 @@
           <t>WEGOVY 2,4MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
+      <c r="C80" s="3" t="n">
+        <v>174.45</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -1406,6 +1650,9 @@
           <t>SPASFON LYOC 160MG LYOT ORAL 5</t>
         </is>
       </c>
+      <c r="C81" s="3" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -1418,6 +1665,9 @@
           <t>WEGOVY 1MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
+      <c r="C82" s="3" t="n">
+        <v>131.21</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -1430,6 +1680,9 @@
           <t>PRIORIX INJ FL+SRG 1 +2AIG</t>
         </is>
       </c>
+      <c r="C83" s="3" t="n">
+        <v>11.4</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -1442,6 +1695,9 @@
           <t>ESTREVA GEL FL-DOS 50G</t>
         </is>
       </c>
+      <c r="C84" s="3" t="n">
+        <v>4.46</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -1454,6 +1710,9 @@
           <t>DEXAFREE 1MG/ML COLLY DOS 30</t>
         </is>
       </c>
+      <c r="C85" s="3" t="n">
+        <v>3.69</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1466,6 +1725,9 @@
           <t>OTIPAX SOL INSTIL AUR FV16G+CG</t>
         </is>
       </c>
+      <c r="C86" s="3" t="n">
+        <v>1.52</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -1478,6 +1740,9 @@
           <t>TRULICITY 3MG INJ STY0,5ML 4</t>
         </is>
       </c>
+      <c r="C87" s="3" t="n">
+        <v>71.42</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -1490,6 +1755,9 @@
           <t>MOUNJARO 10MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
+      <c r="C88" s="3" t="n">
+        <v>301.11</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -1502,6 +1770,9 @@
           <t>PYOSTACINE 500MG CPR BT16</t>
         </is>
       </c>
+      <c r="C89" s="3" t="n">
+        <v>15.92</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -1514,6 +1785,9 @@
           <t>TOCO 500MG CAPS MOL BT30</t>
         </is>
       </c>
+      <c r="C90" s="3" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -1526,6 +1800,9 @@
           <t>UVEDOSE 50000UI CAPS MOL BT2</t>
         </is>
       </c>
+      <c r="C91" s="3" t="n">
+        <v>1.78</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -1538,6 +1815,9 @@
           <t>DOLIPRANE 300MG PDR SACH 12</t>
         </is>
       </c>
+      <c r="C92" s="3" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -1550,6 +1830,9 @@
           <t>THERALENE 5MG CPR PELLIC BT50</t>
         </is>
       </c>
+      <c r="C93" s="3" t="n">
+        <v>1.49</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -1562,6 +1845,9 @@
           <t>FEROGRAD VIT C 500 CPR BT30</t>
         </is>
       </c>
+      <c r="C94" s="3" t="n">
+        <v>1.92</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -1574,6 +1860,9 @@
           <t>LEVOTHYROX 25MCG CPR BT90 EXC</t>
         </is>
       </c>
+      <c r="C95" s="3" t="n">
+        <v>1.26</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -1586,6 +1875,9 @@
           <t>STRESAM GELU BT60</t>
         </is>
       </c>
+      <c r="C96" s="3" t="n">
+        <v>6.98</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -1598,6 +1890,9 @@
           <t>HYLO CONFORT COLLY HYD F10ML T</t>
         </is>
       </c>
+      <c r="C97" s="3" t="n">
+        <v>7.02</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1610,6 +1905,9 @@
           <t>ATURGYL 0,05% NAS FL15ML</t>
         </is>
       </c>
+      <c r="C98" s="3" t="n">
+        <v>1.13</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -1622,6 +1920,9 @@
           <t>OPTILOVA 20MCG/100MCG CPR 28X3</t>
         </is>
       </c>
+      <c r="C99" s="3" t="n">
+        <v>3.23</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -1634,6 +1935,9 @@
           <t>KLIPAL 600MG/50MG CPR BT12</t>
         </is>
       </c>
+      <c r="C100" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -1646,6 +1950,9 @@
           <t>TRULICITY 4,5MG INJ STY0,5ML 4</t>
         </is>
       </c>
+      <c r="C101" s="3" t="n">
+        <v>71.42</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -1658,6 +1965,9 @@
           <t>TIMOFEROL GELU BT30</t>
         </is>
       </c>
+      <c r="C102" s="3" t="n">
+        <v>1.42</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -1670,6 +1980,9 @@
           <t>WEGOVY 1,7MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
+      <c r="C103" s="3" t="n">
+        <v>151.27</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -1682,6 +1995,9 @@
           <t>DOLIPRANE 1000MG CPR EFFV TB8</t>
         </is>
       </c>
+      <c r="C104" s="3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -1694,6 +2010,9 @@
           <t>ASPEGIC AD. 1000MG BUV SACH 20</t>
         </is>
       </c>
+      <c r="C105" s="3" t="n">
+        <v>2.23</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -1706,6 +2025,9 @@
           <t>STAGID 700MG CPR BT100</t>
         </is>
       </c>
+      <c r="C106" s="3" t="n">
+        <v>4.92</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -1718,6 +2040,9 @@
           <t>PREVISCAN 20MG CPR BT30</t>
         </is>
       </c>
+      <c r="C107" s="3" t="n">
+        <v>1.76</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -1730,6 +2055,9 @@
           <t>XYLOCAINE 10MG/ML S/C FL20ML 1</t>
         </is>
       </c>
+      <c r="C108" s="3" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -1742,6 +2070,9 @@
           <t>HEXYON INJ SRG0,5ML 1 + 1AIG</t>
         </is>
       </c>
+      <c r="C109" s="3" t="n">
+        <v>28.94</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -1754,6 +2085,9 @@
           <t>DOLIPRANE 150MG SUP BT10</t>
         </is>
       </c>
+      <c r="C110" s="3" t="n">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -1766,6 +2100,9 @@
           <t>DIPROSONE 0,05% POM TB30G</t>
         </is>
       </c>
+      <c r="C111" s="3" t="n">
+        <v>2.41</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -1778,6 +2115,9 @@
           <t>PAROEX 0,12% BAIN BCHE F300ML</t>
         </is>
       </c>
+      <c r="C112" s="3" t="n">
+        <v>2.02</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -1790,6 +2130,9 @@
           <t>PLAQUENIL 200MG CPR PEL BT30</t>
         </is>
       </c>
+      <c r="C113" s="3" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -1802,6 +2145,9 @@
           <t>POLYDEXA SOL AURIC FL10,5ML</t>
         </is>
       </c>
+      <c r="C114" s="3" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -1814,6 +2160,9 @@
           <t>MELAXOSE PATE ORAL POT P150G+C</t>
         </is>
       </c>
+      <c r="C115" s="3" t="n">
+        <v>3.42</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -1826,6 +2175,9 @@
           <t>GYDRELLE 0,1% CR VAG TB30G</t>
         </is>
       </c>
+      <c r="C116" s="3" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -1838,6 +2190,9 @@
           <t>TOUJEO 300U SOLOSTAR STY1,5ML3</t>
         </is>
       </c>
+      <c r="C117" s="3" t="n">
+        <v>31.08</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -1850,6 +2205,9 @@
           <t>SYSTANE BAL GTT OCUL LUB10ML T</t>
         </is>
       </c>
+      <c r="C118" s="3" t="n">
+        <v>8.52</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -1862,6 +2220,9 @@
           <t>THERALENE 4% BUV GTT FL30ML</t>
         </is>
       </c>
+      <c r="C119" s="3" t="n">
+        <v>1.62</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -1874,6 +2235,9 @@
           <t>LEPTICUR 10MG CPR BT30</t>
         </is>
       </c>
+      <c r="C120" s="3" t="n">
+        <v>3.52</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -1886,6 +2250,9 @@
           <t>XIGDUO 5MG/1000MG CPR BT60</t>
         </is>
       </c>
+      <c r="C121" s="3" t="n">
+        <v>32.37</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -1898,6 +2265,9 @@
           <t>INDOCOLLYRE 0,1% COLLY FL5ML</t>
         </is>
       </c>
+      <c r="C122" s="3" t="n">
+        <v>2.59</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -1910,6 +2280,9 @@
           <t>BAQSIMI 3MG PDR NAS UNIDOS  1</t>
         </is>
       </c>
+      <c r="C123" s="3" t="n">
+        <v>52.41</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -1922,6 +2295,9 @@
           <t>ARTELAC 1,6MG/0,5ML CY DOS 60</t>
         </is>
       </c>
+      <c r="C124" s="3" t="n">
+        <v>4.81</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -1934,6 +2310,9 @@
           <t>ELIQUIS 5MG CPR BT60</t>
         </is>
       </c>
+      <c r="C125" s="3" t="n">
+        <v>52.41</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -1946,6 +2325,9 @@
           <t>UVEDOSE 50000UI CAPS MOL BT4</t>
         </is>
       </c>
+      <c r="C126" s="3" t="n">
+        <v>3.44</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -1958,6 +2340,9 @@
           <t>VITABACT 0,05% CY FL GTT10ML 1</t>
         </is>
       </c>
+      <c r="C127" s="3" t="n">
+        <v>3.91</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -1970,6 +2355,9 @@
           <t>ANTIBIO-SYNALAR AURIC SOL 10ML</t>
         </is>
       </c>
+      <c r="C128" s="3" t="n">
+        <v>1.63</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -1982,6 +2370,9 @@
           <t>MONAZOL 2% CR TB15G</t>
         </is>
       </c>
+      <c r="C129" s="3" t="n">
+        <v>2.24</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -1994,6 +2385,9 @@
           <t>LEVOTHYROX 100MCG CPR BT90 EXC</t>
         </is>
       </c>
+      <c r="C130" s="3" t="n">
+        <v>4.53</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -2006,6 +2400,9 @@
           <t>FLECTOR 1% GEL TB60G - NSFP</t>
         </is>
       </c>
+      <c r="C131" s="3" t="n">
+        <v>1.69</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -2018,6 +2415,9 @@
           <t>LEVOTHYROX 88MCG CPR BT30</t>
         </is>
       </c>
+      <c r="C132" s="3" t="n">
+        <v>1.41</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -2030,6 +2430,9 @@
           <t>DUPHASTON 10MG CPR BT10</t>
         </is>
       </c>
+      <c r="C133" s="3" t="n">
+        <v>2.31</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -2042,6 +2445,9 @@
           <t>DOLIPRANE 500MG CPR BT16</t>
         </is>
       </c>
+      <c r="C134" s="3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -2054,6 +2460,9 @@
           <t>ENTRESTO 49MG/51MG CPR BT56</t>
         </is>
       </c>
+      <c r="C135" s="3" t="n">
+        <v>98.15000000000001</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -2066,6 +2475,9 @@
           <t>ADRIGYL 10000UI/ML GTT FL10ML</t>
         </is>
       </c>
+      <c r="C136" s="3" t="n">
+        <v>1.32</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -2078,6 +2490,9 @@
           <t>COLPOTROPHINE CAPS VAG BT20</t>
         </is>
       </c>
+      <c r="C137" s="3" t="n">
+        <v>3.67</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -2090,6 +2505,9 @@
           <t>ENTRESTO 24MG/26MG CPR BT28</t>
         </is>
       </c>
+      <c r="C138" s="3" t="n">
+        <v>49.06</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -2102,6 +2520,9 @@
           <t>HYLOVIS MULTI GTT FL15ML 1</t>
         </is>
       </c>
+      <c r="C139" s="3" t="n">
+        <v>8.49</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -2114,6 +2535,9 @@
           <t>TRESIBA 200U/ML INJ STYL.3ML 3</t>
         </is>
       </c>
+      <c r="C140" s="3" t="n">
+        <v>49.84</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -2126,6 +2550,9 @@
           <t>PREVENAR 20 INJ SRG0,5ML+AIG 1</t>
         </is>
       </c>
+      <c r="C141" s="3" t="n">
+        <v>50.3</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -2138,6 +2565,9 @@
           <t>BOOSTRIXTETRA INJ SRG0,5ML+A 1</t>
         </is>
       </c>
+      <c r="C142" s="3" t="n">
+        <v>19.17</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -2150,6 +2580,9 @@
           <t>LANTUS 100U/ML INJ SOLO3ML 5</t>
         </is>
       </c>
+      <c r="C143" s="3" t="n">
+        <v>32.31</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -2162,6 +2595,9 @@
           <t>DOLIPRANE 500MG GELU BT16</t>
         </is>
       </c>
+      <c r="C144" s="3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -2174,6 +2610,9 @@
           <t>COSTEC 20+5MG/ML COLLY FL10ML1</t>
         </is>
       </c>
+      <c r="C145" s="3" t="n">
+        <v>12.13</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -2186,6 +2625,9 @@
           <t>LOXEN LP 50MG GELU BT60</t>
         </is>
       </c>
+      <c r="C146" s="3" t="n">
+        <v>9.98</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -2198,6 +2640,9 @@
           <t>DOLIPRANE 200MG SUP BT10</t>
         </is>
       </c>
+      <c r="C147" s="3" t="n">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -2210,6 +2655,9 @@
           <t>ENTRESTO 97MG/103MG CPR BT56</t>
         </is>
       </c>
+      <c r="C148" s="3" t="n">
+        <v>98.15000000000001</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -2222,6 +2670,9 @@
           <t>COLCHICINE MYS 1MG CPR BT30</t>
         </is>
       </c>
+      <c r="C149" s="3" t="n">
+        <v>3.06</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -2234,6 +2685,9 @@
           <t>HYLO LIPID COLLYRE FL3ML1</t>
         </is>
       </c>
+      <c r="C150" s="3" t="n">
+        <v>7.62</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -2246,6 +2700,9 @@
           <t>LAROXYL 25MG CPR BT60</t>
         </is>
       </c>
+      <c r="C151" s="3" t="n">
+        <v>2.89</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -2258,6 +2715,9 @@
           <t>LEVOTHYROX 150MCG CPR BT30 EXC</t>
         </is>
       </c>
+      <c r="C152" s="3" t="n">
+        <v>2.32</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -2270,6 +2730,9 @@
           <t>FLAMMAZINE CR TB50G</t>
         </is>
       </c>
+      <c r="C153" s="3" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -2282,6 +2745,9 @@
           <t>LEVOTHYROX 112MCG CPR BT30</t>
         </is>
       </c>
+      <c r="C154" s="3" t="n">
+        <v>1.77</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -2294,6 +2760,9 @@
           <t>SEPTIVON 1,5% CUTA FL250ML</t>
         </is>
       </c>
+      <c r="C155" s="3" t="n">
+        <v>1.72</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -2306,6 +2775,9 @@
           <t>LACRIFLUID 0,13% CY UNIDOS 60</t>
         </is>
       </c>
+      <c r="C156" s="3" t="n">
+        <v>4.81</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -2318,6 +2790,9 @@
           <t>FERROSTRANE ENF/AD SIR F125ML1</t>
         </is>
       </c>
+      <c r="C157" s="3" t="n">
+        <v>2.01</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -2330,6 +2805,9 @@
           <t>DIPROSALIC LOT FL30ML</t>
         </is>
       </c>
+      <c r="C158" s="3" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -2342,6 +2820,9 @@
           <t>NEFOPAM PANP 30MG CPR PEL BT30</t>
         </is>
       </c>
+      <c r="C159" s="3" t="n">
+        <v>8.84</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -2354,6 +2835,9 @@
           <t>VIT B12 GERDA 250MCG CPR FL24</t>
         </is>
       </c>
+      <c r="C160" s="3" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -2366,6 +2850,9 @@
           <t>RELVAR ELLIPTA 92/22MCG 30DOSX1</t>
         </is>
       </c>
+      <c r="C161" s="3" t="n">
+        <v>25.05</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -2378,6 +2865,9 @@
           <t>BETADINE SCRUB SOL FP125ML</t>
         </is>
       </c>
+      <c r="C162" s="3" t="n">
+        <v>1.33</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -2390,6 +2880,9 @@
           <t>DOLIPRANE 100MG SUP BT10</t>
         </is>
       </c>
+      <c r="C163" s="3" t="n">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -2402,6 +2895,9 @@
           <t>LEVOFREE 0,05% COLLY FL5ML 1</t>
         </is>
       </c>
+      <c r="C164" s="3" t="n">
+        <v>4.64</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -2414,6 +2910,9 @@
           <t>CYTEAL SOL MOUSS FP250ML</t>
         </is>
       </c>
+      <c r="C165" s="3" t="n">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -2426,6 +2925,9 @@
           <t>RYALTRIS 25MCG/600MCG/DOS F30ML1</t>
         </is>
       </c>
+      <c r="C166" s="3" t="n">
+        <v>8.98</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -2438,6 +2940,9 @@
           <t>KEAL 1G SUSP BUV SACH5ML 30</t>
         </is>
       </c>
+      <c r="C167" s="3" t="n">
+        <v>7.89</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -2450,6 +2955,9 @@
           <t>DIPROSONE 0,05% LOT FL30ML</t>
         </is>
       </c>
+      <c r="C168" s="3" t="n">
+        <v>2.41</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -2462,6 +2970,9 @@
           <t>ZALERG 0,25MG/ML COLLY FL5ML</t>
         </is>
       </c>
+      <c r="C169" s="3" t="n">
+        <v>4.24</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -2474,6 +2985,9 @@
           <t>WEGOVY 0,5MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
+      <c r="C170" s="3" t="n">
+        <v>131.21</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -2486,6 +3000,9 @@
           <t>ELIQUIS 2,5MG CPR BT60</t>
         </is>
       </c>
+      <c r="C171" s="3" t="n">
+        <v>52.41</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -2498,6 +3015,9 @@
           <t>VAXELIS INJ SRG0,5ML 1 +1AIG</t>
         </is>
       </c>
+      <c r="C172" s="3" t="n">
+        <v>28.38</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -2510,6 +3030,9 @@
           <t>BETADINE 10% SOL LOC FL125ML</t>
         </is>
       </c>
+      <c r="C173" s="3" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -2522,6 +3045,9 @@
           <t>SOOLANTRA 10MG/G CR TB30G 1</t>
         </is>
       </c>
+      <c r="C174" s="3" t="n">
+        <v>25.82</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -2534,6 +3060,9 @@
           <t>OPTIDRIL 30MCG/150MCG CPR 28X3</t>
         </is>
       </c>
+      <c r="C175" s="3" t="n">
+        <v>3.23</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -2546,6 +3075,9 @@
           <t>MAXIDROL COLLY FL3ML</t>
         </is>
       </c>
+      <c r="C176" s="3" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -2558,6 +3090,9 @@
           <t>SERESTA 10MG CPR BT30</t>
         </is>
       </c>
+      <c r="C177" s="3" t="n">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -2570,6 +3105,9 @@
           <t>ASARED 75MG CPR BT30</t>
         </is>
       </c>
+      <c r="C178" s="3" t="n">
+        <v>1.36</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -2582,6 +3120,9 @@
           <t>ABASAGLAR 100U STY(1-80U) 3ML5</t>
         </is>
       </c>
+      <c r="C179" s="3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -2594,6 +3135,9 @@
           <t>ENGERIX B 20MCG SRG.BACK.1ML 1</t>
         </is>
       </c>
+      <c r="C180" s="3" t="n">
+        <v>13.96</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -2606,6 +3150,9 @@
           <t>RHINOFLUIMUCIL NAS FL NEB 10ML</t>
         </is>
       </c>
+      <c r="C181" s="3" t="n">
+        <v>4.66</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -2618,6 +3165,9 @@
           <t>OZEMPIC 0,5MG INJ STYLO3ML 1</t>
         </is>
       </c>
+      <c r="C182" s="3" t="n">
+        <v>68.25</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -2630,6 +3180,9 @@
           <t>HAVLANE CPR BT20</t>
         </is>
       </c>
+      <c r="C183" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -2642,6 +3195,9 @@
           <t>TOBRADEX COLLY FL5ML</t>
         </is>
       </c>
+      <c r="C184" s="3" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -2654,6 +3210,9 @@
           <t>DEPAKINE CHRONO 500MG CPR TB30</t>
         </is>
       </c>
+      <c r="C185" s="3" t="n">
+        <v>5.96</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -2666,6 +3225,9 @@
           <t>AMYCOR 1% CR LOC TB15G</t>
         </is>
       </c>
+      <c r="C186" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -2678,6 +3240,9 @@
           <t>VOGALENE 5MG SUP SECAB BT10</t>
         </is>
       </c>
+      <c r="C187" s="3" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -2690,6 +3255,9 @@
           <t>LUMIRELAX 500MG CPR BT20</t>
         </is>
       </c>
+      <c r="C188" s="3" t="n">
+        <v>7.42</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -2702,6 +3270,9 @@
           <t>RINOCLENIL 100MCG NAS PULV120D.</t>
         </is>
       </c>
+      <c r="C189" s="3" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -2714,6 +3285,9 @@
           <t>NEREYA COLLY 0,24% FL10ML</t>
         </is>
       </c>
+      <c r="C190" s="3" t="n">
+        <v>6.21</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -2726,6 +3300,9 @@
           <t>EXACYL 500MG CPR PELLIC BT20</t>
         </is>
       </c>
+      <c r="C191" s="3" t="n">
+        <v>2.34</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -2738,6 +3315,9 @@
           <t>LOXEN 20MG CPR BT30</t>
         </is>
       </c>
+      <c r="C192" s="3" t="n">
+        <v>3.21</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -2750,6 +3330,9 @@
           <t>MONOSEPT COLLY DOS 30</t>
         </is>
       </c>
+      <c r="C193" s="3" t="n">
+        <v>2.46</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -2762,6 +3345,9 @@
           <t>SURGAM 200MG CPR BT15</t>
         </is>
       </c>
+      <c r="C194" s="3" t="n">
+        <v>1.69</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -2774,6 +3360,9 @@
           <t>DOLIPRANE 300MG SUP BT10</t>
         </is>
       </c>
+      <c r="C195" s="3" t="n">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -2786,6 +3375,9 @@
           <t>BLEPHACLEAN COMP STER PAUP 20</t>
         </is>
       </c>
+      <c r="C196" s="3" t="n">
+        <v>8.93</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -2798,6 +3390,9 @@
           <t>NERISONE CR TB30G</t>
         </is>
       </c>
+      <c r="C197" s="3" t="n">
+        <v>1.93</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -2810,6 +3405,9 @@
           <t>XOLAAM CPR CROQ BT40</t>
         </is>
       </c>
+      <c r="C198" s="3" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -2822,6 +3420,9 @@
           <t>DIASEPTYL 0,5% SOL PULV 125ML</t>
         </is>
       </c>
+      <c r="C199" s="3" t="n">
+        <v>2.35</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -2834,6 +3435,9 @@
           <t>DULCILARMES 1,5% COLLY DOS 60</t>
         </is>
       </c>
+      <c r="C200" s="3" t="n">
+        <v>4.81</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -2846,9 +3450,12 @@
           <t>LEVOTHYROX 125MCG CPR BT90 EXC</t>
         </is>
       </c>
+      <c r="C201" s="3" t="n">
+        <v>5.64</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B201"/>
+  <autoFilter ref="A1:C201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>